--- a/artfynd/A 51331-2023 artfynd.xlsx
+++ b/artfynd/A 51331-2023 artfynd.xlsx
@@ -1782,7 +1782,7 @@
         <v>512823</v>
       </c>
       <c r="R12" t="n">
-        <v>6564888</v>
+        <v>6564889</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>

--- a/artfynd/A 51331-2023 artfynd.xlsx
+++ b/artfynd/A 51331-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134103169</v>
       </c>
       <c r="B2" t="n">
-        <v>58365</v>
+        <v>58375</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,32 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134102933</v>
+        <v>134103167</v>
       </c>
       <c r="B3" t="n">
-        <v>58298</v>
+        <v>58375</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103008</v>
+        <v>103037</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>bobygge</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512832</v>
+        <v>512823</v>
       </c>
       <c r="R3" t="n">
-        <v>6564886</v>
+        <v>6564887</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -855,12 +855,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,32 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134103167</v>
+        <v>134102933</v>
       </c>
       <c r="B4" t="n">
-        <v>58365</v>
+        <v>58308</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103037</v>
+        <v>103008</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>bobygge</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512823</v>
+        <v>512832</v>
       </c>
       <c r="R4" t="n">
-        <v>6564887</v>
+        <v>6564886</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -961,12 +961,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
         <v>134103636</v>
       </c>
       <c r="B5" t="n">
-        <v>58405</v>
+        <v>58415</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>134103480</v>
       </c>
       <c r="B6" t="n">
-        <v>58648</v>
+        <v>58658</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>134103175</v>
       </c>
       <c r="B7" t="n">
-        <v>58400</v>
+        <v>58410</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>134103433</v>
       </c>
       <c r="B8" t="n">
-        <v>58688</v>
+        <v>58698</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,42 +1417,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134103351</v>
+        <v>134103382</v>
       </c>
       <c r="B9" t="n">
-        <v>58097</v>
+        <v>58519</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>205976</v>
+        <v>102990</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>512782</v>
+        <v>512823</v>
       </c>
       <c r="R9" t="n">
-        <v>6564898</v>
+        <v>6564887</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1491,12 +1491,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1523,42 +1523,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134103382</v>
+        <v>134103351</v>
       </c>
       <c r="B10" t="n">
-        <v>58509</v>
+        <v>58107</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102990</v>
+        <v>205976</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>512823</v>
+        <v>512782</v>
       </c>
       <c r="R10" t="n">
-        <v>6564887</v>
+        <v>6564898</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1597,12 +1597,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1632,7 +1632,7 @@
         <v>134103634</v>
       </c>
       <c r="B11" t="n">
-        <v>58405</v>
+        <v>58415</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>134103453</v>
       </c>
       <c r="B12" t="n">
-        <v>58688</v>
+        <v>58698</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>134103423</v>
       </c>
       <c r="B13" t="n">
-        <v>58688</v>
+        <v>58698</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>134103461</v>
       </c>
       <c r="B14" t="n">
-        <v>58688</v>
+        <v>58698</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 51331-2023 artfynd.xlsx
+++ b/artfynd/A 51331-2023 artfynd.xlsx
@@ -1417,42 +1417,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134103382</v>
+        <v>134103351</v>
       </c>
       <c r="B9" t="n">
-        <v>58519</v>
+        <v>58107</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102990</v>
+        <v>205976</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>512823</v>
+        <v>512782</v>
       </c>
       <c r="R9" t="n">
-        <v>6564887</v>
+        <v>6564898</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1491,12 +1491,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1523,42 +1523,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134103351</v>
+        <v>134103382</v>
       </c>
       <c r="B10" t="n">
-        <v>58107</v>
+        <v>58519</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>205976</v>
+        <v>102990</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>512782</v>
+        <v>512823</v>
       </c>
       <c r="R10" t="n">
-        <v>6564898</v>
+        <v>6564887</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1597,12 +1597,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134103634</v>
+        <v>134103453</v>
       </c>
       <c r="B11" t="n">
-        <v>58415</v>
+        <v>58698</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1640,16 +1640,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102999</v>
+        <v>103055</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>512829</v>
+        <v>512823</v>
       </c>
       <c r="R11" t="n">
-        <v>6564887</v>
+        <v>6564889</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1703,12 +1703,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134103453</v>
+        <v>134103634</v>
       </c>
       <c r="B12" t="n">
-        <v>58698</v>
+        <v>58415</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,16 +1746,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103055</v>
+        <v>102999</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>512823</v>
+        <v>512829</v>
       </c>
       <c r="R12" t="n">
-        <v>6564889</v>
+        <v>6564887</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1809,12 +1809,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 51331-2023 artfynd.xlsx
+++ b/artfynd/A 51331-2023 artfynd.xlsx
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134103453</v>
+        <v>134103634</v>
       </c>
       <c r="B11" t="n">
-        <v>58698</v>
+        <v>58415</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1640,16 +1640,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103055</v>
+        <v>102999</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>512823</v>
+        <v>512829</v>
       </c>
       <c r="R11" t="n">
-        <v>6564889</v>
+        <v>6564887</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1703,12 +1703,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134103634</v>
+        <v>134103453</v>
       </c>
       <c r="B12" t="n">
-        <v>58415</v>
+        <v>58698</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,16 +1746,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102999</v>
+        <v>103055</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>512829</v>
+        <v>512823</v>
       </c>
       <c r="R12" t="n">
-        <v>6564887</v>
+        <v>6564888</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1809,12 +1809,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 51331-2023 artfynd.xlsx
+++ b/artfynd/A 51331-2023 artfynd.xlsx
@@ -781,32 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134103167</v>
+        <v>134102933</v>
       </c>
       <c r="B3" t="n">
-        <v>58375</v>
+        <v>58308</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103037</v>
+        <v>103008</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>bobygge</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512823</v>
+        <v>512832</v>
       </c>
       <c r="R3" t="n">
-        <v>6564887</v>
+        <v>6564886</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -855,12 +855,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,32 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134102933</v>
+        <v>134103167</v>
       </c>
       <c r="B4" t="n">
-        <v>58308</v>
+        <v>58375</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103008</v>
+        <v>103037</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>bobygge</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512832</v>
+        <v>512823</v>
       </c>
       <c r="R4" t="n">
-        <v>6564886</v>
+        <v>6564887</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -961,12 +961,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1782,7 +1782,7 @@
         <v>512823</v>
       </c>
       <c r="R12" t="n">
-        <v>6564889</v>
+        <v>6564888</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>

--- a/artfynd/A 51331-2023 artfynd.xlsx
+++ b/artfynd/A 51331-2023 artfynd.xlsx
@@ -781,32 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134102933</v>
+        <v>134103167</v>
       </c>
       <c r="B3" t="n">
-        <v>58308</v>
+        <v>58375</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103008</v>
+        <v>103037</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>bobygge</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512832</v>
+        <v>512823</v>
       </c>
       <c r="R3" t="n">
-        <v>6564886</v>
+        <v>6564887</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -855,12 +855,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,32 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134103167</v>
+        <v>134102933</v>
       </c>
       <c r="B4" t="n">
-        <v>58375</v>
+        <v>58308</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103037</v>
+        <v>103008</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>bobygge</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512823</v>
+        <v>512832</v>
       </c>
       <c r="R4" t="n">
-        <v>6564887</v>
+        <v>6564886</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -961,12 +961,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134103453</v>
+        <v>134103634</v>
       </c>
       <c r="B11" t="n">
-        <v>58698</v>
+        <v>58415</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1640,16 +1640,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103055</v>
+        <v>102999</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>512823</v>
+        <v>512829</v>
       </c>
       <c r="R11" t="n">
-        <v>6564888</v>
+        <v>6564887</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1703,12 +1703,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134103634</v>
+        <v>134103453</v>
       </c>
       <c r="B12" t="n">
-        <v>58415</v>
+        <v>58698</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,16 +1746,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102999</v>
+        <v>103055</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>512829</v>
+        <v>512823</v>
       </c>
       <c r="R12" t="n">
-        <v>6564887</v>
+        <v>6564889</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1809,12 +1809,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 51331-2023 artfynd.xlsx
+++ b/artfynd/A 51331-2023 artfynd.xlsx
@@ -1417,42 +1417,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134103382</v>
+        <v>134103351</v>
       </c>
       <c r="B9" t="n">
-        <v>58519</v>
+        <v>58107</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102990</v>
+        <v>205976</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>512823</v>
+        <v>512782</v>
       </c>
       <c r="R9" t="n">
-        <v>6564887</v>
+        <v>6564898</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1491,12 +1491,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1523,42 +1523,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134103351</v>
+        <v>134103382</v>
       </c>
       <c r="B10" t="n">
-        <v>58107</v>
+        <v>58519</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>205976</v>
+        <v>102990</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>512782</v>
+        <v>512823</v>
       </c>
       <c r="R10" t="n">
-        <v>6564898</v>
+        <v>6564887</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1597,12 +1597,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134103634</v>
+        <v>134103453</v>
       </c>
       <c r="B11" t="n">
-        <v>58415</v>
+        <v>58698</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1640,16 +1640,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102999</v>
+        <v>103055</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>512829</v>
+        <v>512823</v>
       </c>
       <c r="R11" t="n">
-        <v>6564887</v>
+        <v>6564888</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1703,12 +1703,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134103453</v>
+        <v>134103634</v>
       </c>
       <c r="B12" t="n">
-        <v>58698</v>
+        <v>58415</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,16 +1746,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103055</v>
+        <v>102999</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>512823</v>
+        <v>512829</v>
       </c>
       <c r="R12" t="n">
-        <v>6564889</v>
+        <v>6564887</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1809,12 +1809,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 51331-2023 artfynd.xlsx
+++ b/artfynd/A 51331-2023 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134103169</v>
+        <v>134103382</v>
       </c>
       <c r="B2" t="n">
-        <v>58375</v>
+        <v>58519</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103037</v>
+        <v>102990</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>512782</v>
+        <v>512823</v>
       </c>
       <c r="R2" t="n">
-        <v>6564898</v>
+        <v>6564887</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,27 +781,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134103167</v>
+        <v>134103634</v>
       </c>
       <c r="B3" t="n">
-        <v>58375</v>
+        <v>58415</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103037</v>
+        <v>102999</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>bobygge</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512823</v>
+        <v>512829</v>
       </c>
       <c r="R3" t="n">
         <v>6564887</v>
@@ -855,12 +855,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134102933</v>
+        <v>134103636</v>
       </c>
       <c r="B4" t="n">
-        <v>58308</v>
+        <v>58415</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103008</v>
+        <v>102999</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512832</v>
+        <v>512823</v>
       </c>
       <c r="R4" t="n">
-        <v>6564886</v>
+        <v>6564887</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -961,12 +961,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134103636</v>
+        <v>134103175</v>
       </c>
       <c r="B5" t="n">
-        <v>58415</v>
+        <v>58410</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102999</v>
+        <v>103001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512823</v>
+        <v>512825</v>
       </c>
       <c r="R5" t="n">
-        <v>6564887</v>
+        <v>6564886</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134103480</v>
+        <v>134102933</v>
       </c>
       <c r="B6" t="n">
-        <v>58658</v>
+        <v>58308</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1110,16 +1110,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103044</v>
+        <v>103008</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1143,7 +1143,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>512833</v>
+        <v>512832</v>
       </c>
       <c r="R6" t="n">
         <v>6564886</v>
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134103175</v>
+        <v>134103167</v>
       </c>
       <c r="B7" t="n">
-        <v>58410</v>
+        <v>58375</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103001</v>
+        <v>103037</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>bobygge</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>512825</v>
+        <v>512823</v>
       </c>
       <c r="R7" t="n">
-        <v>6564886</v>
+        <v>6564887</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1311,27 +1311,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134103433</v>
+        <v>134103169</v>
       </c>
       <c r="B8" t="n">
-        <v>58698</v>
+        <v>58375</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103055</v>
+        <v>103037</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>512831</v>
+        <v>512782</v>
       </c>
       <c r="R8" t="n">
-        <v>6564886</v>
+        <v>6564898</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1385,12 +1385,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1417,37 +1417,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134103351</v>
+        <v>134103480</v>
       </c>
       <c r="B9" t="n">
-        <v>58107</v>
+        <v>58658</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>205976</v>
+        <v>103044</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>512782</v>
+        <v>512833</v>
       </c>
       <c r="R9" t="n">
-        <v>6564898</v>
+        <v>6564886</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1491,12 +1491,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1523,32 +1523,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134103382</v>
+        <v>134103422</v>
       </c>
       <c r="B10" t="n">
-        <v>58519</v>
+        <v>58698</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102990</v>
+        <v>103055</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>512823</v>
+        <v>512843</v>
       </c>
       <c r="R10" t="n">
-        <v>6564887</v>
+        <v>6564881</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1597,12 +1597,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1629,7 +1629,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134103453</v>
+        <v>134103433</v>
       </c>
       <c r="B11" t="n">
         <v>58698</v>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>512823</v>
+        <v>512831</v>
       </c>
       <c r="R11" t="n">
-        <v>6564888</v>
+        <v>6564886</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1703,12 +1703,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134103634</v>
+        <v>134103453</v>
       </c>
       <c r="B12" t="n">
-        <v>58415</v>
+        <v>58698</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,16 +1746,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102999</v>
+        <v>103055</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>512829</v>
+        <v>512823</v>
       </c>
       <c r="R12" t="n">
-        <v>6564887</v>
+        <v>6564889</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1809,12 +1809,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1841,7 +1841,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134103423</v>
+        <v>134103461</v>
       </c>
       <c r="B13" t="n">
         <v>58698</v>
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>512843</v>
+        <v>512782</v>
       </c>
       <c r="R13" t="n">
-        <v>6564881</v>
+        <v>6564897</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1915,12 +1915,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1947,27 +1947,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134103461</v>
+        <v>134103351</v>
       </c>
       <c r="B14" t="n">
-        <v>58698</v>
+        <v>58107</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103055</v>
+        <v>205976</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1977,12 +1977,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1994,7 +1994,7 @@
         <v>512782</v>
       </c>
       <c r="R14" t="n">
-        <v>6564897</v>
+        <v>6564898</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>

--- a/artfynd/A 51331-2023 artfynd.xlsx
+++ b/artfynd/A 51331-2023 artfynd.xlsx
@@ -1782,7 +1782,7 @@
         <v>512823</v>
       </c>
       <c r="R12" t="n">
-        <v>6564889</v>
+        <v>6564888</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>

--- a/artfynd/A 51331-2023 artfynd.xlsx
+++ b/artfynd/A 51331-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134103382</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134103634</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134103636</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134103175</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102933</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134103167</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134103169</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1520,6 +1560,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134103480</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1626,6 +1671,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134103422</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1732,6 +1782,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134103433</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1838,6 +1893,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134103453</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1944,6 +2004,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134103461</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2050,8 +2115,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134103351</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>